--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,28 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,30 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,226 +413,258 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="65" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Finding ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Vulnerability Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>CWE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>OWASP</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CWE Mapping</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>OWASP Mapping</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>File Path</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>SEC-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Broken Authentication</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>CWE-306</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>OWASP A01:2021</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>backend/app/auth.py</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>/api/upload</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Optional API Key verification allows unauthenticated access</t>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Permissive CORS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CWE-942</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OWASP A05:2021</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>backend/app/main.py</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>SEC-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>CSV Formula Injection</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>CWE-1236</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>OWASP A03:2021</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>backend/app/routes/download.py</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>/api/download/{job_id}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Unescaped formula prefixes in exported CSV files</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Path Traversal in Upload</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CWE-22</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OWASP A01:2021</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>backend/app/routes/upload.py</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>/api/upload</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>SEC-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Information Disclosure</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>CWE-209</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>OWASP A05:2021</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>backend/app/routes/forecast.py</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>/api/forecast</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Internal traceback exposed in model error responses</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Unrestricted Rate Limiting</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CWE-770</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OWASP A04:2021</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>backend/app/main.py</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>SEC-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Rate Limit Memory Storage</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>CWE-400</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>OWASP A04:2021</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Interactive API Docs Exposed</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CWE-200</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OWASP A05:2021</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>backend/app/main.py</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>All Endpoints</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>In-memory rate limiting does not scale across multiple workers</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>/docs</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SEC-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Missing Security Headers</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CWE-693</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OWASP A05:2021</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>backend/app/main.py</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
     </row>

--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,46 +428,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Finding ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Vulnerability Type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CWE Mapping</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>OWASP Mapping</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>File Path</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -466,12 +497,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Permissive CORS</t>
+          <t>Missing CORS Restriction</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -481,7 +512,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OWASP A05:2021</t>
+          <t>A05:2021 - Security Misconfiguration</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,12 +522,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>All Endpoints</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Cross-origin resource access</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Remediated</t>
         </is>
       </c>
     </row>
@@ -508,37 +544,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Path Traversal in Upload</t>
+          <t>Rate Limiting Absent</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CWE-22</t>
+          <t>CWE-770</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OWASP A01:2021</t>
+          <t>A04:2021 - Insecure Design</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>backend/app/routes/upload.py</t>
+          <t>backend/app/routers/auth.py</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>/api/upload</t>
+          <t>/api/v1/auth/login</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Brute-force authentication risks</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Remediated</t>
         </is>
       </c>
     </row>
@@ -555,32 +596,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unrestricted Rate Limiting</t>
+          <t>Path Traversal Risk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CWE-770</t>
+          <t>CWE-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OWASP A04:2021</t>
+          <t>A01:2021 - Broken Access Control</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>backend/app/main.py</t>
+          <t>backend/app/routers/upload.py</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>/api/v1/upload/csv</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Arbitrary file reading potential</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Remediated</t>
         </is>
       </c>
     </row>
@@ -607,7 +653,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OWASP A05:2021</t>
+          <t>A05:2021 - Security Misconfiguration</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -622,49 +668,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Resolved</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SEC-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Missing Security Headers</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CWE-693</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>OWASP A05:2021</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>backend/app/main.py</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Resolved</t>
+          <t>Information disclosure</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Remediated</t>
         </is>
       </c>
     </row>
